--- a/artfynd/A 26919-2025 artfynd.xlsx
+++ b/artfynd/A 26919-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136194310</v>
       </c>
       <c r="B3" t="n">
-        <v>92123</v>
+        <v>92126</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26919-2025 artfynd.xlsx
+++ b/artfynd/A 26919-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136194310</v>
       </c>
       <c r="B3" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26919-2025 artfynd.xlsx
+++ b/artfynd/A 26919-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136194310</v>
       </c>
       <c r="B3" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26919-2025 artfynd.xlsx
+++ b/artfynd/A 26919-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136194310</v>
       </c>
       <c r="B3" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
